--- a/artfynd/A 10419-2025 artfynd.xlsx
+++ b/artfynd/A 10419-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16733379</v>
+        <v>105035342</v>
       </c>
       <c r="B2" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3767</v>
+        <v>1985</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
+          <t>Syd Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701698.3987734467</v>
+        <v>701801</v>
       </c>
       <c r="R2" t="n">
-        <v>6358328.129826836</v>
+        <v>6358290</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,55 +754,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16733371</v>
+        <v>16733375</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701760.9019247449</v>
+        <v>701747</v>
       </c>
       <c r="R3" t="n">
-        <v>6358379.343870253</v>
+        <v>6358344</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,28 +845,17 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16733388</v>
+        <v>16733389</v>
       </c>
       <c r="B4" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701696.4756962986</v>
+        <v>701696</v>
       </c>
       <c r="R4" t="n">
-        <v>6358323.167577803</v>
+        <v>6358323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16733386</v>
+        <v>16733368</v>
       </c>
       <c r="B5" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701696.4756962986</v>
+        <v>701763</v>
       </c>
       <c r="R5" t="n">
-        <v>6358323.167577803</v>
+        <v>6358383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1039,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1071,7 @@
         <v>16733374</v>
       </c>
       <c r="B6" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701746.9270022252</v>
+        <v>701747</v>
       </c>
       <c r="R6" t="n">
-        <v>6358344.0420425</v>
+        <v>6358344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1136,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16733377</v>
+        <v>16733382</v>
       </c>
       <c r="B7" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701713.2426346039</v>
+        <v>701659</v>
       </c>
       <c r="R7" t="n">
-        <v>6358334.810407825</v>
+        <v>6358336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1233,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16733378</v>
+        <v>16733386</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701713.2426346039</v>
+        <v>701696</v>
       </c>
       <c r="R8" t="n">
-        <v>6358334.810407825</v>
+        <v>6358323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,28 +1330,17 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1470,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16733385</v>
+        <v>105035373</v>
       </c>
       <c r="B9" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
+          <t>Syd Graunvik, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701696.4756962986</v>
+        <v>701792</v>
       </c>
       <c r="R9" t="n">
-        <v>6358323.167577803</v>
+        <v>6358295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,22 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,49 +1444,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Gotlands län</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16733368</v>
+        <v>16733377</v>
       </c>
       <c r="B10" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701763.4186553897</v>
+        <v>701713</v>
       </c>
       <c r="R10" t="n">
-        <v>6358383.253703186</v>
+        <v>6358335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,19 +1528,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,37 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16733380</v>
+        <v>16733385</v>
       </c>
       <c r="B11" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701698.3987734467</v>
+        <v>701696</v>
       </c>
       <c r="R11" t="n">
-        <v>6358328.129826836</v>
+        <v>6358323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,19 +1625,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,15 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16733389</v>
+        <v>16733380</v>
       </c>
       <c r="B12" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701696.4756962986</v>
+        <v>701698</v>
       </c>
       <c r="R12" t="n">
-        <v>6358323.167577803</v>
+        <v>6358328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,19 +1722,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,15 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16733375</v>
+        <v>16733388</v>
       </c>
       <c r="B13" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701746.9270022252</v>
+        <v>701696</v>
       </c>
       <c r="R13" t="n">
-        <v>6358344.0420425</v>
+        <v>6358323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,19 +1819,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,15 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105035342</v>
+        <v>16733379</v>
       </c>
       <c r="B14" t="n">
-        <v>85057</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,37 +1859,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1985</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Syd Graunvik, Gtl</t>
+          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>701800.5608460719</v>
+        <v>701698</v>
       </c>
       <c r="R14" t="n">
-        <v>6358289.3572056</v>
+        <v>6358328</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,22 +1922,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,76 +1936,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105035373</v>
+        <v>16733371</v>
       </c>
       <c r="B15" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Syd Graunvik, Gtl</t>
+          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>701791.6454806969</v>
+        <v>701761</v>
       </c>
       <c r="R15" t="n">
-        <v>6358294.326098105</v>
+        <v>6358379</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,22 +2019,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,25 +2033,218 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16733378</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701713</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6358335</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16733381</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lojsta Rovide 1:10, Backhagen, södra delen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701659</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6358336</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Gotlands län</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10419-2025 artfynd.xlsx
+++ b/artfynd/A 10419-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105035373</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733389</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733368</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733374</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733386</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733385</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733380</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733379</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733371</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733378</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,8 +2325,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733381</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>